--- a/artfynd/A 45751-2022 artfynd.xlsx
+++ b/artfynd/A 45751-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45751-2022 artfynd.xlsx
+++ b/artfynd/A 45751-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12966,6 +12966,127 @@
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>115090833</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57388</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Mjölkarkullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>545170</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7208822</v>
+      </c>
+      <c r="S111" t="n">
+        <v>25</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-03-09</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45751-2022 artfynd.xlsx
+++ b/artfynd/A 45751-2022 artfynd.xlsx
@@ -11258,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="AE95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG95" t="b">
         <v>0</v>

--- a/artfynd/A 45751-2022 artfynd.xlsx
+++ b/artfynd/A 45751-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104448215</v>
+        <v>104448089</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544896.2137077579</v>
+        <v>544686</v>
       </c>
       <c r="R2" t="n">
-        <v>7209104.732144362</v>
+        <v>7209002</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104448237</v>
+        <v>104448217</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545112.7827474645</v>
+        <v>544907</v>
       </c>
       <c r="R3" t="n">
-        <v>7208986.564118225</v>
+        <v>7209121</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104448221</v>
+        <v>104448090</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544976.9426280342</v>
+        <v>544677</v>
       </c>
       <c r="R4" t="n">
-        <v>7209116.95042091</v>
+        <v>7209133</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,44 +989,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104448127</v>
+        <v>104448249</v>
       </c>
       <c r="B5" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545206.6181962834</v>
+        <v>545145</v>
       </c>
       <c r="R5" t="n">
-        <v>7208916.897736466</v>
+        <v>7208779</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104448133</v>
+        <v>104448092</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545173.8998402577</v>
+        <v>544679</v>
       </c>
       <c r="R6" t="n">
-        <v>7208811.459038346</v>
+        <v>7209125</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104448247</v>
+        <v>104448220</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,39 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545137.7613967523</v>
+        <v>544978</v>
       </c>
       <c r="R7" t="n">
-        <v>7208819.797995987</v>
+        <v>7209117</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104448230</v>
+        <v>104448113</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,39 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545033.6363252356</v>
+        <v>544903</v>
       </c>
       <c r="R8" t="n">
-        <v>7208981.559004026</v>
+        <v>7209066</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,22 +1417,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104448114</v>
+        <v>104448120</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,39 +1435,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544902.7295058358</v>
+        <v>545025</v>
       </c>
       <c r="R9" t="n">
-        <v>7209065.902965735</v>
+        <v>7209033</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,15 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104448204</v>
+        <v>104448122</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,12 +1551,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544807.1798686465</v>
+        <v>545049</v>
       </c>
       <c r="R10" t="n">
-        <v>7209278.558947135</v>
+        <v>7208989</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,22 +1631,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104448122</v>
+        <v>104448200</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,12 +1658,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545048.7818635893</v>
+        <v>544785</v>
       </c>
       <c r="R11" t="n">
-        <v>7208988.558084854</v>
+        <v>7209285</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,22 +1738,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104448241</v>
+        <v>104448204</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,39 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545191.9026220856</v>
+        <v>544807</v>
       </c>
       <c r="R12" t="n">
-        <v>7208909.481055484</v>
+        <v>7209278</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104448111</v>
+        <v>104448209</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544898.541670422</v>
+        <v>544909</v>
       </c>
       <c r="R13" t="n">
-        <v>7209090.804204857</v>
+        <v>7209258</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,22 +1952,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104448186</v>
+        <v>104448232</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2079,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544641.1089380177</v>
+        <v>545059</v>
       </c>
       <c r="R14" t="n">
-        <v>7209053.510483052</v>
+        <v>7209017</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,15 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104448129</v>
+        <v>104448234</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2191,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545199.796322964</v>
+        <v>545084</v>
       </c>
       <c r="R15" t="n">
-        <v>7208919.756318019</v>
+        <v>7209019</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,22 +2166,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104448199</v>
+        <v>104448236</v>
       </c>
       <c r="B16" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544704.8096533468</v>
+        <v>545113</v>
       </c>
       <c r="R16" t="n">
-        <v>7209297.330092201</v>
+        <v>7208986</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,55 +2280,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104448131</v>
+        <v>104448109</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>918</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545163.8114594943</v>
+        <v>544884</v>
       </c>
       <c r="R17" t="n">
-        <v>7208834.156895503</v>
+        <v>7209211</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,37 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104448065</v>
+        <v>104448130</v>
       </c>
       <c r="B18" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544676.1018506673</v>
+        <v>545189</v>
       </c>
       <c r="R18" t="n">
-        <v>7208979.98673008</v>
+        <v>7208904</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,37 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104448202</v>
+        <v>104448195</v>
       </c>
       <c r="B19" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>918</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544818.1338463057</v>
+        <v>544646</v>
       </c>
       <c r="R19" t="n">
-        <v>7209282.531514477</v>
+        <v>7209228</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,15 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104448213</v>
+        <v>104448065</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,39 +2612,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544910.5430058276</v>
+        <v>544676</v>
       </c>
       <c r="R20" t="n">
-        <v>7209165.876759264</v>
+        <v>7208980</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2796,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2826,22 +2701,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104448210</v>
+        <v>104448103</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2873,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544912.5606385139</v>
+        <v>544772</v>
       </c>
       <c r="R21" t="n">
-        <v>7209256.874831839</v>
+        <v>7209291</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2908,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,22 +2808,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104448191</v>
+        <v>104448116</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2961,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2985,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544667.9848351494</v>
+        <v>544946</v>
       </c>
       <c r="R22" t="n">
-        <v>7209125.843794131</v>
+        <v>7209044</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3020,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3050,22 +2915,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104448108</v>
+        <v>104448182</v>
       </c>
       <c r="B23" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3073,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3097,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544900.9884985755</v>
+        <v>544606</v>
       </c>
       <c r="R23" t="n">
-        <v>7209293.932939484</v>
+        <v>7209029</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3132,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3142,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,22 +3022,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104448207</v>
+        <v>104448187</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3185,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3209,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544875.791410959</v>
+        <v>544632</v>
       </c>
       <c r="R24" t="n">
-        <v>7209307.515475415</v>
+        <v>7209063</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3244,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3281,37 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104448104</v>
+        <v>104448189</v>
       </c>
       <c r="B25" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3321,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544805.062324547</v>
+        <v>544654</v>
       </c>
       <c r="R25" t="n">
-        <v>7209278.527111103</v>
+        <v>7209080</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3356,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3386,22 +3236,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104448242</v>
+        <v>104448222</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3409,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3433,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545187.2111042729</v>
+        <v>544978</v>
       </c>
       <c r="R26" t="n">
-        <v>7208883.597698364</v>
+        <v>7209120</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3468,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3478,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,15 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104448211</v>
+        <v>104448225</v>
       </c>
       <c r="B27" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3521,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3545,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544915.5825978143</v>
+        <v>545014</v>
       </c>
       <c r="R27" t="n">
-        <v>7209253.112480801</v>
+        <v>7209059</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3580,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3617,15 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104448222</v>
+        <v>104448235</v>
       </c>
       <c r="B28" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3657,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544978.1685363105</v>
+        <v>545120</v>
       </c>
       <c r="R28" t="n">
-        <v>7209119.930753333</v>
+        <v>7209013</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3692,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,37 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104448195</v>
+        <v>104448245</v>
       </c>
       <c r="B29" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>918</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3769,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544645.7046622684</v>
+        <v>545180</v>
       </c>
       <c r="R29" t="n">
-        <v>7209227.479258246</v>
+        <v>7208857</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3804,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,37 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104448193</v>
+        <v>104448107</v>
       </c>
       <c r="B30" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3881,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544664.5573436178</v>
+        <v>544896</v>
       </c>
       <c r="R30" t="n">
-        <v>7209156.679764028</v>
+        <v>7209290</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3916,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,22 +3771,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104448200</v>
+        <v>104448184</v>
       </c>
       <c r="B31" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3969,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3993,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544785.0493474201</v>
+        <v>544618</v>
       </c>
       <c r="R31" t="n">
-        <v>7209285.418914746</v>
+        <v>7209023</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4028,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4065,15 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104448117</v>
+        <v>104448201</v>
       </c>
       <c r="B32" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4081,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4105,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>544995.2760947248</v>
+        <v>544801</v>
       </c>
       <c r="R32" t="n">
-        <v>7209024.98574343</v>
+        <v>7209289</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4140,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4170,22 +3985,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104448189</v>
+        <v>104448211</v>
       </c>
       <c r="B33" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4193,21 +4003,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4217,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>544653.8520900322</v>
+        <v>544915</v>
       </c>
       <c r="R33" t="n">
-        <v>7209079.511980167</v>
+        <v>7209253</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4252,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,15 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104448198</v>
+        <v>104448218</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4305,39 +4110,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>544666.2972059409</v>
+        <v>544949</v>
       </c>
       <c r="R34" t="n">
-        <v>7209266.712937431</v>
+        <v>7209117</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4369,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4379,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,15 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104448098</v>
+        <v>104448237</v>
       </c>
       <c r="B35" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4422,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4446,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>544757.0978288992</v>
+        <v>545113</v>
       </c>
       <c r="R35" t="n">
-        <v>7209284.999007641</v>
+        <v>7208986</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4481,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4511,22 +4306,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104448109</v>
+        <v>104448097</v>
       </c>
       <c r="B36" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4534,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>918</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4558,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>544884.0135896757</v>
+        <v>544727</v>
       </c>
       <c r="R36" t="n">
-        <v>7209211.595942447</v>
+        <v>7209270</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4593,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4603,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,37 +4420,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104448121</v>
+        <v>104448098</v>
       </c>
       <c r="B37" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4670,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545051.6827717974</v>
+        <v>544757</v>
       </c>
       <c r="R37" t="n">
-        <v>7208992.833304031</v>
+        <v>7209285</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4705,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4715,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4742,37 +4527,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104448120</v>
+        <v>104448105</v>
       </c>
       <c r="B38" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4782,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545025.2263633549</v>
+        <v>544807</v>
       </c>
       <c r="R38" t="n">
-        <v>7209033.477535402</v>
+        <v>7209276</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4817,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4854,37 +4634,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104448187</v>
+        <v>104448106</v>
       </c>
       <c r="B39" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4894,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>544632.0625485505</v>
+        <v>544855</v>
       </c>
       <c r="R39" t="n">
-        <v>7209063.53002118</v>
+        <v>7209290</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4929,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4939,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4959,44 +4734,39 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104448132</v>
+        <v>104448108</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5006,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545158.8952382217</v>
+        <v>544901</v>
       </c>
       <c r="R40" t="n">
-        <v>7208823.080229984</v>
+        <v>7209294</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5041,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5051,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5078,37 +4848,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>104448228</v>
+        <v>104448117</v>
       </c>
       <c r="B41" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5118,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545013.5760884343</v>
+        <v>544995</v>
       </c>
       <c r="R41" t="n">
-        <v>7208991.411289581</v>
+        <v>7209025</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5153,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5163,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5183,44 +4948,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104448107</v>
+        <v>104448133</v>
       </c>
       <c r="B42" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5230,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>544895.9701414828</v>
+        <v>545174</v>
       </c>
       <c r="R42" t="n">
-        <v>7209289.626395609</v>
+        <v>7208811</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5265,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5302,37 +5062,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>104448092</v>
+        <v>104448194</v>
       </c>
       <c r="B43" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5342,10 +5097,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>544679.0093096327</v>
+        <v>544657</v>
       </c>
       <c r="R43" t="n">
-        <v>7209125.162806781</v>
+        <v>7209163</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5377,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5387,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5407,26 +5162,21 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104448194</v>
+        <v>104448202</v>
       </c>
       <c r="B44" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5454,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>544656.8387994667</v>
+        <v>544818</v>
       </c>
       <c r="R44" t="n">
-        <v>7209162.910775719</v>
+        <v>7209283</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5489,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5499,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5526,37 +5276,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104448243</v>
+        <v>104448206</v>
       </c>
       <c r="B45" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5566,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>545188.9053647552</v>
+        <v>544842</v>
       </c>
       <c r="R45" t="n">
-        <v>7208883.623383556</v>
+        <v>7209300</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5601,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5611,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5638,37 +5383,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104448229</v>
+        <v>104448212</v>
       </c>
       <c r="B46" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5678,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>545034.9069786202</v>
+        <v>544899</v>
       </c>
       <c r="R46" t="n">
-        <v>7208981.578202493</v>
+        <v>7209150</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5713,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5723,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5750,37 +5490,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104448102</v>
+        <v>104448104</v>
       </c>
       <c r="B47" t="n">
-        <v>76487</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1794</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rödskaftad svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis haematopus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5790,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>544773.2229022409</v>
+        <v>544805</v>
       </c>
       <c r="R47" t="n">
-        <v>7209283.125745311</v>
+        <v>7209278</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5825,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5835,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5846,21 +5581,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>granticka</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5877,15 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104448123</v>
+        <v>104448112</v>
       </c>
       <c r="B48" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5893,39 +5608,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>545054.590066312</v>
+        <v>544905</v>
       </c>
       <c r="R48" t="n">
-        <v>7208996.685480261</v>
+        <v>7209081</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5957,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5967,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5994,15 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104448128</v>
+        <v>104448183</v>
       </c>
       <c r="B49" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,39 +5715,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>545203.5955312387</v>
+        <v>544615</v>
       </c>
       <c r="R49" t="n">
-        <v>7208920.660228761</v>
+        <v>7209024</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6074,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6084,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6104,22 +5804,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104448208</v>
+        <v>104448203</v>
       </c>
       <c r="B50" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,16 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6146,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>544925.0236918877</v>
+        <v>544798</v>
       </c>
       <c r="R50" t="n">
-        <v>7209273.140395933</v>
+        <v>7209273</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6181,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6191,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,15 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>104448091</v>
+        <v>104448238</v>
       </c>
       <c r="B51" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6258,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>544674.1285466334</v>
+        <v>545113</v>
       </c>
       <c r="R51" t="n">
-        <v>7209139.898685812</v>
+        <v>7208989</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6293,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6303,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6323,22 +6018,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104448219</v>
+        <v>104448199</v>
       </c>
       <c r="B52" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,39 +6036,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>544950.9732020437</v>
+        <v>544705</v>
       </c>
       <c r="R52" t="n">
-        <v>7209125.444123078</v>
+        <v>7209297</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6410,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6420,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6447,37 +6132,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104448188</v>
+        <v>104448185</v>
       </c>
       <c r="B53" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6487,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>544653.8520900322</v>
+        <v>544618</v>
       </c>
       <c r="R53" t="n">
-        <v>7209079.511980167</v>
+        <v>7209023</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6522,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6532,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6559,37 +6239,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104448236</v>
+        <v>104448226</v>
       </c>
       <c r="B54" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6599,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>545112.7827474645</v>
+        <v>545019</v>
       </c>
       <c r="R54" t="n">
-        <v>7208986.564118225</v>
+        <v>7209032</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6634,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6644,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6671,37 +6346,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104448100</v>
+        <v>104448102</v>
       </c>
       <c r="B55" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78335</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>1794</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rödskaftad svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis haematopus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6711,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>544763.8294799794</v>
+        <v>544773</v>
       </c>
       <c r="R55" t="n">
-        <v>7209288.061769824</v>
+        <v>7209283</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6746,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6767,6 +6437,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>granticka</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6783,37 +6468,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104448182</v>
+        <v>104448134</v>
       </c>
       <c r="B56" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6823,10 +6503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>544606.3095948448</v>
+        <v>545155</v>
       </c>
       <c r="R56" t="n">
-        <v>7209029.294300293</v>
+        <v>7208778</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6858,7 +6538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6868,14 +6548,14 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -6888,22 +6568,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>104448093</v>
+        <v>104448228</v>
       </c>
       <c r="B57" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6911,21 +6586,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6935,10 +6610,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>544662.5819101686</v>
+        <v>545014</v>
       </c>
       <c r="R57" t="n">
-        <v>7209231.963148281</v>
+        <v>7208991</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6970,7 +6645,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6980,7 +6655,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7000,44 +6675,39 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>104448089</v>
+        <v>104448124</v>
       </c>
       <c r="B58" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>2809</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7047,10 +6717,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>544685.5137269264</v>
+        <v>545055</v>
       </c>
       <c r="R58" t="n">
-        <v>7209002.13086726</v>
+        <v>7208995</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7082,7 +6752,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7092,7 +6762,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7119,37 +6789,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>104448232</v>
+        <v>104448115</v>
       </c>
       <c r="B59" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>2813</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7159,10 +6824,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>545059.3656753162</v>
+        <v>544905</v>
       </c>
       <c r="R59" t="n">
-        <v>7209017.068156028</v>
+        <v>7209008</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7194,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7204,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7224,44 +6889,39 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>104448216</v>
+        <v>104448094</v>
       </c>
       <c r="B60" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7271,10 +6931,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>544908.241221198</v>
+        <v>544663</v>
       </c>
       <c r="R60" t="n">
-        <v>7209121.838117518</v>
+        <v>7209235</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7306,7 +6966,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7316,7 +6976,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7336,44 +6996,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>104448245</v>
+        <v>104448121</v>
       </c>
       <c r="B61" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7383,10 +7038,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>545180.4208944232</v>
+        <v>545052</v>
       </c>
       <c r="R61" t="n">
-        <v>7208856.412845219</v>
+        <v>7208993</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7418,7 +7073,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7428,7 +7083,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7448,26 +7103,21 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>104448231</v>
+        <v>104448096</v>
       </c>
       <c r="B62" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -7495,10 +7145,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>545056.4008526315</v>
+        <v>544704</v>
       </c>
       <c r="R62" t="n">
-        <v>7209017.023335998</v>
+        <v>7209259</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7530,7 +7180,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7540,7 +7190,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7560,22 +7210,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>104448249</v>
+        <v>104448111</v>
       </c>
       <c r="B63" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7583,21 +7228,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7607,10 +7252,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>545145.58368159</v>
+        <v>544898</v>
       </c>
       <c r="R63" t="n">
-        <v>7208778.869466584</v>
+        <v>7209091</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7642,7 +7287,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7652,7 +7297,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7672,44 +7317,39 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>104448136</v>
+        <v>104448119</v>
       </c>
       <c r="B64" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7719,10 +7359,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>545155.4157454747</v>
+        <v>545023</v>
       </c>
       <c r="R64" t="n">
-        <v>7208773.094036656</v>
+        <v>7209039</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7754,7 +7394,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7764,7 +7404,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7791,37 +7431,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>104448220</v>
+        <v>104448126</v>
       </c>
       <c r="B65" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7831,10 +7466,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>544978.2132236199</v>
+        <v>545097</v>
       </c>
       <c r="R65" t="n">
-        <v>7209116.969595399</v>
+        <v>7208993</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7866,7 +7501,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7876,7 +7511,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7896,44 +7531,39 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>104448201</v>
+        <v>104448132</v>
       </c>
       <c r="B66" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7943,10 +7573,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>544801.0854149396</v>
+        <v>545159</v>
       </c>
       <c r="R66" t="n">
-        <v>7209289.467785183</v>
+        <v>7208823</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7978,7 +7608,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7988,7 +7618,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8008,44 +7638,39 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>104448113</v>
+        <v>104448186</v>
       </c>
       <c r="B67" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8055,10 +7680,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>544902.7295058358</v>
+        <v>544641</v>
       </c>
       <c r="R67" t="n">
-        <v>7209065.902965735</v>
+        <v>7209053</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8090,7 +7715,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8100,7 +7725,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8120,22 +7745,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>104448130</v>
+        <v>104448188</v>
       </c>
       <c r="B68" t="n">
-        <v>90160</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8143,21 +7763,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8167,10 +7787,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>545188.6039217307</v>
+        <v>544654</v>
       </c>
       <c r="R68" t="n">
-        <v>7208903.506945121</v>
+        <v>7209080</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8202,7 +7822,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8212,7 +7832,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8232,26 +7852,21 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>104448205</v>
+        <v>104448191</v>
       </c>
       <c r="B69" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -8279,10 +7894,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>544842.000135007</v>
+        <v>544668</v>
       </c>
       <c r="R69" t="n">
-        <v>7209301.08355129</v>
+        <v>7209126</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8314,7 +7929,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8324,7 +7939,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8351,37 +7966,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>104448206</v>
+        <v>104448196</v>
       </c>
       <c r="B70" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8391,10 +8001,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>544842.0128643222</v>
+        <v>544668</v>
       </c>
       <c r="R70" t="n">
-        <v>7209300.237557892</v>
+        <v>7209268</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8426,7 +8036,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8436,7 +8046,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8463,19 +8073,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>104448196</v>
+        <v>104448205</v>
       </c>
       <c r="B71" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -8503,10 +8108,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>544668.3957381088</v>
+        <v>544842</v>
       </c>
       <c r="R71" t="n">
-        <v>7209268.013678833</v>
+        <v>7209301</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8538,7 +8143,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8548,7 +8153,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8575,15 +8180,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>104448185</v>
+        <v>104448210</v>
       </c>
       <c r="B72" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8591,21 +8191,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8615,10 +8215,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>544617.4167321071</v>
+        <v>544912</v>
       </c>
       <c r="R72" t="n">
-        <v>7209023.113595042</v>
+        <v>7209257</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8650,7 +8250,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8660,7 +8260,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8690,16 +8290,11 @@
         <v>104448214</v>
       </c>
       <c r="B73" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -8727,10 +8322,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>544895.3666406332</v>
+        <v>544895</v>
       </c>
       <c r="R73" t="n">
-        <v>7209104.719384626</v>
+        <v>7209105</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8799,37 +8394,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>104448106</v>
+        <v>104448216</v>
       </c>
       <c r="B74" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8839,10 +8429,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>544854.8708318966</v>
+        <v>544908</v>
       </c>
       <c r="R74" t="n">
-        <v>7209290.276815521</v>
+        <v>7209122</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8874,7 +8464,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8884,7 +8474,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8904,22 +8494,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>104448183</v>
+        <v>104448221</v>
       </c>
       <c r="B75" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8927,21 +8512,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8951,10 +8536,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>544614.4329201904</v>
+        <v>544977</v>
       </c>
       <c r="R75" t="n">
-        <v>7209024.338322049</v>
+        <v>7209117</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8986,7 +8571,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8996,7 +8581,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9023,37 +8608,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>104448192</v>
+        <v>104448229</v>
       </c>
       <c r="B76" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9063,10 +8643,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>544667.9848351494</v>
+        <v>545035</v>
       </c>
       <c r="R76" t="n">
-        <v>7209125.843794131</v>
+        <v>7208981</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9098,7 +8678,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9108,7 +8688,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9135,37 +8715,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>104448218</v>
+        <v>104448231</v>
       </c>
       <c r="B77" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9175,10 +8750,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>544948.9767640202</v>
+        <v>545057</v>
       </c>
       <c r="R77" t="n">
-        <v>7209117.374764728</v>
+        <v>7209017</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9210,7 +8785,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9220,7 +8795,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9247,19 +8822,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>104448119</v>
+        <v>104448233</v>
       </c>
       <c r="B78" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -9287,10 +8857,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>545023.0191813642</v>
+        <v>545086</v>
       </c>
       <c r="R78" t="n">
-        <v>7209039.368023805</v>
+        <v>7209020</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9322,7 +8892,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9332,7 +8902,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9352,22 +8922,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>104448203</v>
+        <v>104448242</v>
       </c>
       <c r="B79" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9375,21 +8940,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9399,10 +8964,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>544798.37520156</v>
+        <v>545187</v>
       </c>
       <c r="R79" t="n">
-        <v>7209272.503242459</v>
+        <v>7208884</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9434,7 +8999,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9444,7 +9009,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9471,37 +9036,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>104448094</v>
+        <v>104448248</v>
       </c>
       <c r="B80" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9511,10 +9071,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>544662.5375360776</v>
+        <v>545148</v>
       </c>
       <c r="R80" t="n">
-        <v>7209234.924191227</v>
+        <v>7208779</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9546,7 +9106,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9556,7 +9116,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9576,62 +9136,52 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>104448060</v>
+        <v>115090846</v>
       </c>
       <c r="B81" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>544677.8808831286</v>
+        <v>545112</v>
       </c>
       <c r="R81" t="n">
-        <v>7209059.138982792</v>
+        <v>7208701</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9658,22 +9208,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9693,22 +9243,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>104448105</v>
+        <v>104448100</v>
       </c>
       <c r="B82" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9716,21 +9261,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9740,10 +9285,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>544807.2243865917</v>
+        <v>544764</v>
       </c>
       <c r="R82" t="n">
-        <v>7209275.597946977</v>
+        <v>7209288</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9775,7 +9320,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9785,7 +9330,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9812,15 +9357,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>104448240</v>
+        <v>104448129</v>
       </c>
       <c r="B83" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9828,39 +9368,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>545168.8773170905</v>
+        <v>545200</v>
       </c>
       <c r="R83" t="n">
-        <v>7208975.142628134</v>
+        <v>7208920</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9892,7 +9427,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9902,7 +9437,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9922,44 +9457,39 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>104448238</v>
+        <v>104448193</v>
       </c>
       <c r="B84" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9969,10 +9499,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>545112.737926885</v>
+        <v>544665</v>
       </c>
       <c r="R84" t="n">
-        <v>7208989.525405847</v>
+        <v>7209157</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10004,7 +9534,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10014,7 +9544,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10041,37 +9571,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>104448234</v>
+        <v>104448127</v>
       </c>
       <c r="B85" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10081,10 +9606,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>545084.3292980186</v>
+        <v>545207</v>
       </c>
       <c r="R85" t="n">
-        <v>7209019.138189217</v>
+        <v>7208917</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10116,7 +9641,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10126,7 +9651,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10146,44 +9671,39 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>104448225</v>
+        <v>104448224</v>
       </c>
       <c r="B86" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10193,10 +9713,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>545013.824499569</v>
+        <v>544993</v>
       </c>
       <c r="R86" t="n">
-        <v>7209059.116203019</v>
+        <v>7209077</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -10228,7 +9748,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10238,7 +9758,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10265,50 +9785,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>104448116</v>
+        <v>104448114</v>
       </c>
       <c r="B87" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>544946.2622130144</v>
+        <v>544903</v>
       </c>
       <c r="R87" t="n">
-        <v>7209044.556488577</v>
+        <v>7209066</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10340,7 +9860,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10350,7 +9870,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10377,15 +9897,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>104448118</v>
+        <v>104448060</v>
       </c>
       <c r="B88" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10422,10 +9937,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>545025.3605647938</v>
+        <v>544678</v>
       </c>
       <c r="R88" t="n">
-        <v>7209024.593795271</v>
+        <v>7209059</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10457,7 +9972,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10467,7 +9982,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10494,15 +10009,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>104448096</v>
+        <v>104448099</v>
       </c>
       <c r="B89" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10510,34 +10020,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>544704.5336996</v>
+        <v>544756</v>
       </c>
       <c r="R89" t="n">
-        <v>7209259.24740426</v>
+        <v>7209282</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10569,7 +10084,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10579,7 +10094,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10606,15 +10121,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>104448126</v>
+        <v>104448118</v>
       </c>
       <c r="B90" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10622,34 +10132,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>545096.579018575</v>
+        <v>545026</v>
       </c>
       <c r="R90" t="n">
-        <v>7208993.512250907</v>
+        <v>7209024</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10681,7 +10196,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10691,7 +10206,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10718,50 +10233,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>104448226</v>
+        <v>104448123</v>
       </c>
       <c r="B91" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>545019.3095302128</v>
+        <v>545054</v>
       </c>
       <c r="R91" t="n">
-        <v>7209032.541896733</v>
+        <v>7208997</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10793,7 +10308,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10803,7 +10318,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10823,22 +10338,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>104448248</v>
+        <v>104448128</v>
       </c>
       <c r="B92" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10846,34 +10356,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>545148.5487414653</v>
+        <v>545203</v>
       </c>
       <c r="R92" t="n">
-        <v>7208778.914374547</v>
+        <v>7208921</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10905,7 +10420,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10915,7 +10430,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10935,22 +10450,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>104448103</v>
+        <v>104448131</v>
       </c>
       <c r="B93" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10958,34 +10468,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>544771.83163849</v>
+        <v>545164</v>
       </c>
       <c r="R93" t="n">
-        <v>7209291.143631073</v>
+        <v>7208834</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11017,7 +10532,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11027,7 +10542,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11054,15 +10569,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>104448184</v>
+        <v>104448198</v>
       </c>
       <c r="B94" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11070,34 +10580,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>544617.4167321071</v>
+        <v>544666</v>
       </c>
       <c r="R94" t="n">
-        <v>7209023.113595042</v>
+        <v>7209267</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11129,7 +10644,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11139,7 +10654,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11166,50 +10681,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>104448134</v>
+        <v>104448213</v>
       </c>
       <c r="B95" t="n">
-        <v>89734</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>545155.338838816</v>
+        <v>544911</v>
       </c>
       <c r="R95" t="n">
-        <v>7208778.170890867</v>
+        <v>7209166</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11241,7 +10756,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11251,14 +10766,14 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="b">
         <v>0</v>
@@ -11271,22 +10786,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>104448235</v>
+        <v>104448219</v>
       </c>
       <c r="B96" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11294,34 +10804,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>545120.4395581379</v>
+        <v>544951</v>
       </c>
       <c r="R96" t="n">
-        <v>7209012.491338341</v>
+        <v>7209126</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11353,7 +10868,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11363,7 +10878,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11390,15 +10905,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>104448244</v>
+        <v>104448223</v>
       </c>
       <c r="B97" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11406,29 +10916,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>545176.4997706829</v>
+        <v>544994</v>
       </c>
       <c r="R97" t="n">
-        <v>7208863.547073201</v>
+        <v>7209116</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11460,7 +10980,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11470,7 +10990,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11497,15 +11017,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>104448233</v>
+        <v>104448230</v>
       </c>
       <c r="B98" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11513,34 +11028,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>545086.4278294176</v>
+        <v>545034</v>
       </c>
       <c r="R98" t="n">
-        <v>7209020.439332813</v>
+        <v>7208981</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11572,7 +11092,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11582,7 +11102,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11609,15 +11129,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>104448212</v>
+        <v>104448240</v>
       </c>
       <c r="B99" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11625,34 +11140,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>544898.926469713</v>
+        <v>545169</v>
       </c>
       <c r="R99" t="n">
-        <v>7209149.623442063</v>
+        <v>7208975</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11684,7 +11204,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11694,7 +11214,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11721,50 +11241,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>104448090</v>
+        <v>104448241</v>
       </c>
       <c r="B100" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>544677.1947047329</v>
+        <v>545192</v>
       </c>
       <c r="R100" t="n">
-        <v>7209133.17480823</v>
+        <v>7208910</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11796,7 +11316,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11806,7 +11326,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11826,22 +11346,17 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>104448217</v>
+        <v>104448247</v>
       </c>
       <c r="B101" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11849,34 +11364,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>544906.9833753759</v>
+        <v>545138</v>
       </c>
       <c r="R101" t="n">
-        <v>7209120.972928626</v>
+        <v>7208820</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11908,7 +11428,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11918,7 +11438,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11945,15 +11465,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>104448223</v>
+        <v>104448250</v>
       </c>
       <c r="B102" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11981,7 +11496,7 @@
       <c r="I102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11990,10 +11505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>544994.3265923868</v>
+        <v>545141</v>
       </c>
       <c r="R102" t="n">
-        <v>7209115.943450642</v>
+        <v>7208732</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12025,7 +11540,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12035,7 +11550,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12062,15 +11577,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>104448250</v>
+        <v>115090833</v>
       </c>
       <c r="B103" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12078,27 +11588,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12107,10 +11621,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>545141.2118784774</v>
+        <v>545170</v>
       </c>
       <c r="R103" t="n">
-        <v>7208731.831268298</v>
+        <v>7208821</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12137,22 +11651,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12172,57 +11686,61 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>104448112</v>
+        <v>104448239</v>
       </c>
       <c r="B104" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1209</v>
+        <v>103031</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>544904.6241303418</v>
+        <v>545158</v>
       </c>
       <c r="R104" t="n">
-        <v>7209080.740882721</v>
+        <v>7208976</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12254,7 +11772,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12264,7 +11782,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12284,22 +11802,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>104448209</v>
+        <v>104448208</v>
       </c>
       <c r="B105" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12307,21 +11820,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>6040186</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12331,10 +11844,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>544909.1534203939</v>
+        <v>544925</v>
       </c>
       <c r="R105" t="n">
-        <v>7209258.09278373</v>
+        <v>7209273</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12366,7 +11879,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12376,7 +11889,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12403,15 +11916,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>104448099</v>
+        <v>104448244</v>
       </c>
       <c r="B106" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12419,39 +11927,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Mjölkarkullen, Ås lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>544756.2952805033</v>
+        <v>545176</v>
       </c>
       <c r="R106" t="n">
-        <v>7209282.025293653</v>
+        <v>7208863</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12483,7 +11986,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12493,7 +11996,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12513,579 +12016,10 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
+          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>104448101</v>
-      </c>
-      <c r="B107" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Mjölkarkullen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q107" t="n">
-        <v>544771.1180706379</v>
-      </c>
-      <c r="R107" t="n">
-        <v>7209282.247934973</v>
-      </c>
-      <c r="S107" t="n">
-        <v>25</v>
-      </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AD107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT107" t="inlineStr"/>
-      <c r="AW107" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>104448124</v>
-      </c>
-      <c r="B108" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>2809</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Mörk husmossa</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Mjölkarkullen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q108" t="n">
-        <v>545054.6156450681</v>
-      </c>
-      <c r="R108" t="n">
-        <v>7208994.99332043</v>
-      </c>
-      <c r="S108" t="n">
-        <v>25</v>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AD108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT108" t="inlineStr"/>
-      <c r="AW108" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>104448097</v>
-      </c>
-      <c r="B109" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Mjölkarkullen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q109" t="n">
-        <v>544727.2382629412</v>
-      </c>
-      <c r="R109" t="n">
-        <v>7209270.588584871</v>
-      </c>
-      <c r="S109" t="n">
-        <v>25</v>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AD109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT109" t="inlineStr"/>
-      <c r="AW109" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Eva Mårtensson, Yasmine Kindlund</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>104448224</v>
-      </c>
-      <c r="B110" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Mjölkarkullen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q110" t="n">
-        <v>544992.7964371622</v>
-      </c>
-      <c r="R110" t="n">
-        <v>7209076.993119142</v>
-      </c>
-      <c r="S110" t="n">
-        <v>25</v>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AD110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT110" t="inlineStr"/>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Yasmine Kindlund, Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>115090833</v>
-      </c>
-      <c r="B111" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Mjölkarkullen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q111" t="n">
-        <v>545170</v>
-      </c>
-      <c r="R111" t="n">
-        <v>7208821</v>
-      </c>
-      <c r="S111" t="n">
-        <v>25</v>
-      </c>
-      <c r="T111" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y111" t="inlineStr">
-        <is>
-          <t>2024-03-09</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>2024-03-09</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="AD111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT111" t="inlineStr"/>
-      <c r="AW111" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
